--- a/AAII_Financials/Quarterly/EDU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EDU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>EDU</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45808</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45169</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45260</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45169</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45077</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44895</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44804</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44712</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44620</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44530</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44347</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44255</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44165</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44074</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43982</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43890</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43799</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43708</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43616</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43524</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43434</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43343</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43251</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43159</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43069</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42978</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42886</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42794</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42704</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1529500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1417300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1191400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1523000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1243200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1183100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1038600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1435400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1136700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1100000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>1100000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>860600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>754200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>638200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>744800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>524000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>614100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1967100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1212000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1190500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>887700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>986400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>798500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>923200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>785200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1071800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>842900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>796700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>597100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>859800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>701000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>618100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>467200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>661200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>486400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>437800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>341200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>534100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>717300</v>
+      </c>
+      <c r="E9" s="3">
         <v>656200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>556900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>637800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>569900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>531600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>498300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>583500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>542400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>441200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
         <v>441200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>391600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>369600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>336200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>312100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>247800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>372700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1133700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>578800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>539500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>453700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>464900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>391100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>398600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>359000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>440200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>371200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>337500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>300100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>367400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>299500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>268800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>227300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>270200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>199300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>183600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>163400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>812200</v>
+      </c>
+      <c r="E10" s="3">
         <v>761200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>634600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>885200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>673300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>651500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>540300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>851900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>594300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>658800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>658800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>469000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>384600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>302000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>432700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>276200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>241400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>833400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>633200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>651000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>434000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>521500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>407400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>524600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>426200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>631600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>471700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>459200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>297000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>492400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>401500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>349300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>239900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>391000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>287100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>254200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>177800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>330700</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,132 +1476,138 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-7800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>65600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>19400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-7200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-7200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>209000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>101500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-100</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1000</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3">
         <v>2300</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>36500</v>
+        <v>44700</v>
       </c>
       <c r="E15" s="3">
         <v>36500</v>
@@ -1596,7 +1619,7 @@
         <v>36500</v>
       </c>
       <c r="H15" s="3">
-        <v>26700</v>
+        <v>36500</v>
       </c>
       <c r="I15" s="3">
         <v>26700</v>
@@ -1608,23 +1631,23 @@
         <v>26700</v>
       </c>
       <c r="L15" s="3">
+        <v>26700</v>
+      </c>
+      <c r="M15" s="3">
         <v>30700</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
-        <v>30700</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>30700</v>
       </c>
       <c r="P15" s="3">
+        <v>30700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>48600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1697,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1443700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1237000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1125100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1212200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1191500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1058500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1019400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1142300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1126200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>894900</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>894900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>812500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>687700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>640700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>666800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>838600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>755300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2688500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1354600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1089000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>919800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>836100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>788200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>806000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>759900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>825600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>765900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>700900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>625600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>698500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>645400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>559700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>480300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>500100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>436900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>380300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>341000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>381500</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E18" s="3">
         <v>180300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>66300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>310800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>51600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>124500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>293200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>205100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>205100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>48100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>66500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>78000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-314600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-141200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-721400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-142600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>101500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>150300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>117200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>25300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>246200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>77000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>95800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-28500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>161300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>55600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>58400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>161100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>49500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>57500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,172 +2051,176 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-15800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-20500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>92500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-17900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-24700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-39300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>110300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-26200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>-26200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>87600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-40400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>26600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>31600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>143000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>36800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>82900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>53700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>65600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>62500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>62800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>16400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>34500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>33900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>30700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>24600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>23600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>24900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>21200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>19800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>15900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E21" s="3">
         <v>229900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>118600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>367800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>169200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>70700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>359200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-73000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>262000</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>262000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>155500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2256,13 +2293,16 @@
       <c r="AO21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>8</v>
@@ -2270,81 +2310,81 @@
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
         <v>4100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>6700</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>4600</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
         <v>1600</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2354,8 +2394,8 @@
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
@@ -2375,246 +2415,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E23" s="3">
         <v>194600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>80700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>339100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>142200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>320500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>34200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>238600</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>238600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>59400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>113600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>109600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-175700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-104400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-638500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-95600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>167100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>30400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>213100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>22000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>151700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>59200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>254900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>69500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>126400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-27900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>147900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>80200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>80300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>10500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>186000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>70700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>77300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>16100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>166600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E24" s="3">
         <v>54700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>91500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>52600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>77600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62500</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>62500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>19300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>113800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-29300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>47000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>59100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>36200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>33300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>14100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>30600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>29500</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>25700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>16100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>13400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>26900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>14500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>10600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>2900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E26" s="3">
         <v>139900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>56300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>247500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>89700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>31800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>243000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>176100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>176100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>39900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>94300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>86200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-181300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-121300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-908000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-66300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>120100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>23600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>154000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>118500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>45200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>204000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>38900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>97000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-27900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>122200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>64100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>66900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>7500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>159100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>56300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>66700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>13200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>143900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E27" s="3">
         <v>126800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>45500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>240700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>87300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>31900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>245400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>165400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>165400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>81600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>66000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-189300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-122400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1761800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-45500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>151300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>53900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>174700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>13200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>137700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>53400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>209000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>43200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>97400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-25800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>123200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>65100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>68400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>158400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>55400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>67600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>10400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>141100</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,246 +3513,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-69700</v>
+      </c>
+      <c r="E32" s="3">
         <v>13100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>15800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>20500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-92500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>17900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>24700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>39300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-110300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>26200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>26200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-87600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>40400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-26600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-31600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-143000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-36800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-82900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-53700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-65600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-62500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-62800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-34500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-33900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-30700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>13400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-21900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-23600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-24900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-21200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-19800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E33" s="3">
         <v>126800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>45500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>240700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>87300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>31900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>245400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>165400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>165400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>29000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>81600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>66000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-189300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-122400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1761800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-45500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>151300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>53900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>174700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>13200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>137700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>53400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>209000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>43200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>97400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-25800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>123200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>65100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>68400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>158400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>55400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>67600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>10400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>141100</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E35" s="3">
         <v>126800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>45500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>240700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>87300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>31900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>245400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>165400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>165400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>29000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>81600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>66000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-189300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-122400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1761800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-45500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>151300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>53900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>174700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>13200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>137700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>53400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>209000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>43200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>97400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-25800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>123200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>65100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>68400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>158400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>55400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>67600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>10400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>141100</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45808</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45169</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45260</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45169</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45077</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44895</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44804</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44712</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44620</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44530</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44347</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44255</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44165</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44074</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43982</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43890</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43799</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43708</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43616</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43524</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43434</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43343</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43251</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43159</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43069</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42978</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42886</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42794</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42704</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,489 +4218,502 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1821200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1783400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1842900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1282300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1612400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1418800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1418200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1147000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1389400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1748900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O41" s="3">
         <v>1748900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1663000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1329500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1029900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1103900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1148600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1466800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1026900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1612200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1569800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2643200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1047600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>915100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1057100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1047600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>973200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1414200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>844900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>842900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>833100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>983300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>721500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>818100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>838900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>641000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>535900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>520700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>591100</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3291800</v>
+      </c>
+      <c r="E42" s="3">
         <v>3019000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3094900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3386400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2965600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2876000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3294400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3660000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3385700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2368100</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>2368100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2333600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2981600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3178800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3147000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3042300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2943200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3777900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4648800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4508500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3451400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3070200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2603100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2510200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2569900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2362300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1777400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1889400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1795200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1798900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1731500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1796000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1610300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1554000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1524800</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1434600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1377600</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1271700</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>251600</v>
+      </c>
+      <c r="E43" s="3">
         <v>42600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>42900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>42500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>189900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>39300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>41100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>39100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>193800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>43800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O43" s="3">
         <v>43800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>136800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>37400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>38300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>26600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>39700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>43900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>34300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>34300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>41900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>45000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>50300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>45900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>18700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>6200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>8700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>8200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>105800</v>
+      </c>
+      <c r="E44" s="3">
         <v>86000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>92100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>86300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>80900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>85700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>92700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>95400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>92800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>63300</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
         <v>63300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>52700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>62700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>74600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>43900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>27900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>30700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>34400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>31200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>35700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>30700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>31100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>31300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>32800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>28900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>29600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>29000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>34100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>35100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>36300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>40200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>42200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>34800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>31800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>31700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>28200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>30200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>129700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4622,589 +4721,604 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>123500</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>120800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>98600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>295800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>263200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>215400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>207400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>281400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>269200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>247700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>226800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>201300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>199400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>237800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>223800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>223000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>199700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>225900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>207800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>218600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>182100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>165500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>188100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>144700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>119400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>119000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>122600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5831800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5427100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5587900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5310600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5187700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4872900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5371700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5491300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5388900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4571000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O46" s="3">
         <v>4571000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4413900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4700800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4617400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4584600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4474000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4692100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5155000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6574200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6374200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6364200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4384400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3756400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3879800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3915200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3638300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3466200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3020200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2906600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2905600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2941900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2732000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2657400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2575200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2326300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2126400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2059300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2006400</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>830400</v>
+      </c>
+      <c r="E47" s="3">
         <v>808000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>761100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>755900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>744100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>778700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>501100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>467800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>525000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>854700</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
         <v>854700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>862300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>429200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>400900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>429700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>441300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>584400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>536200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>541900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>558800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>510100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>457800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>453800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>475500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>469500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>482600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>455700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>474300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>437800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>459000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>475700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>336800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>276500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>261100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>243000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>197200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>205100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1734400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1636300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1579100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1595200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1561200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1452000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1425800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1405400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1161900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>828700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O48" s="3">
         <v>828700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>799300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>786300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>759600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>824900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>933800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1205200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1774700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2722600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2539300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2341400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2231000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2097900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1979400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1864000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1768500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>532000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>524600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>488900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>474100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>449600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>418800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>365000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>333900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>282800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>259400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>249600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>250700</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E49" s="3">
         <v>111900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>110200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>111100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>111800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>122100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>124100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>127800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>127100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>130000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N49" s="3">
+      <c r="N49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O49" s="3">
         <v>130000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>134000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>138700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>134700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>71600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>73600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>77000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>150200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>78100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>109000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>103300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>101200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>90600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>93200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>90000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>96100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>100000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>113300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>92200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>50700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>44100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>45100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>40800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>25700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>21800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>23600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>15800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>16500</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>178700</v>
+      </c>
+      <c r="E52" s="3">
         <v>175500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>172100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>166400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>102800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>141100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>140300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>145200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>256100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>234500</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" s="3">
         <v>234500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>127000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>77700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>111000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>109200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>112000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>110600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7752300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>234300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>196000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>158900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>154900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>158100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>214000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>155400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>82800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>92700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>86600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>77100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>71800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>66500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>37300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>41500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>51100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>52700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>40400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8792000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8244400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8290900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8012900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7805500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7447200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7634500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7709100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7531700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6674700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O54" s="3">
         <v>6674700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6392500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6164300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6023600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6019900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6034700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6669200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7614300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10151100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9777300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9478000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7329300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6556900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6641900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6494100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6068200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4646600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4219000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4002600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3961200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3977700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3574700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3377100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3237400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2925000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2659400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2570200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2510700</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,187 +6014,191 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>126900</v>
+      </c>
+      <c r="E57" s="3">
         <v>108500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>94500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>85200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>80500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>85600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>92100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>102000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>105700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>76600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>76600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>69800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>89500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>81700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>43500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>22500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>28000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1413200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>38500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>30200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>33000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>34400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>34700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>39500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>32800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>36900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>34500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>37900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>36500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>36300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>39900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>34300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>26900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>24300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>21500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>27100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E58" s="3">
         <v>273300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>262100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>260200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>256000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>239600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>218600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>222400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>199900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>163900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O58" s="3">
         <v>163900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>155800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>152600</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V58" s="3">
         <v>300</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
@@ -6122,336 +6256,345 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2878400</v>
+      </c>
+      <c r="E59" s="3">
         <v>2101800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2454400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2120400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2435500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1939200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2136200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1939000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2204200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1573200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>1573200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1675100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1265000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1841300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1725100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1687600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1861900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5327300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3433000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3146000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3181100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2742900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2444600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2517100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2635400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2383800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1971700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1816100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1773300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1694500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1711000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1455100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1472700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1347700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1178400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1024500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>992900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>915200</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3889700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3278600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3554400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3211900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3289800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2942600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3134100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2965500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3000900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2366400</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O60" s="3">
         <v>2366400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2251000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1954300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1923000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1768700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1710100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1889900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2426300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3471400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3176200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3214000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2777400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2479400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2556600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2668200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2420700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2006200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1854000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1809800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1730800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1750900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1495900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1507000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1374600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1202700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1046000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1019900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>939600</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>563800</v>
+      </c>
+      <c r="E61" s="3">
         <v>533700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>517800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>523800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>547800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>499100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>504200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>488000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>462400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>305700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>305700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>302800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>314500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>44200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>65400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>113200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>190000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>297600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>297500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>300000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>298200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>117900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>117500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>117200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>95200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>96500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>51100</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -6479,8 +6622,11 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6523,83 +6669,86 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3">
         <v>342300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>390400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>465600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>561500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2004300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1363800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1258900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1147400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1104600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1089800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1061900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>953100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>888500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>18800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>18700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>18200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>12100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4467600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3826400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4086200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3754500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3851800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3471700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3652900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3470200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3482700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2695200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O66" s="3">
         <v>2695200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2577700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2287700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2416400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2313800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2329200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2646500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3509700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5237800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4861900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4774100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4304200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3823600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3887100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3899700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3562700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2285900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2145500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2051000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1965300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1986100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1545800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1556000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1418800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1244000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1085100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1056600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>975400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,13 +7764,16 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>2560200</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>8</v>
@@ -7607,38 +7781,38 @@
       <c r="F72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3">
         <v>2273600</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>2000100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3">
         <v>1690500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -7673,47 +7847,50 @@
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE72" s="3">
         <v>1953200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI72" s="3">
         <v>1616100</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AL72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM72" s="3">
         <v>1391100</v>
       </c>
-      <c r="AM72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3986300</v>
+      </c>
+      <c r="E76" s="3">
         <v>4086100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3886000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3952700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3661900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3686200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3699800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3968600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3775900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3739100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O76" s="3">
         <v>3739100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3604300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3725500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3607200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3706100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3705500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4022800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4104600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4913300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4915300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4703900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3025100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2733300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2754800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2594500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2505600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2360700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2073500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1951700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1996000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1991600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2028900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1821100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1818600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1680900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1574300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1513600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1535300</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45808</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45169</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45260</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45169</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45077</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44895</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44804</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44712</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44620</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44530</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44347</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44255</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44165</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44074</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43982</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43890</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43799</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43708</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43616</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43524</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43434</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43343</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43251</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43159</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43069</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42978</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42886</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42794</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42704</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E81" s="3">
         <v>126800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>45500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>240700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>87300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>31900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>245400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>165400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>165400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>29000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>81600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>66000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-189300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-122400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1761800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-45500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>151300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>53900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>174700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>13200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>137700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>53400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>209000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>43200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>97400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-25800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>123200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>65100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>68400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>158400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>55400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>67600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>10400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>141100</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,13 +8791,14 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>139800</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
@@ -8607,38 +8806,38 @@
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>100600</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>117000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>192300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>192300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8712,8 +8911,11 @@
       <c r="AO83" s="3">
         <v>0</v>
       </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,74 +9521,77 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>518700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>323500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>192300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>399100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>313300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>183200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>376800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>335800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>335800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>421600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>190500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>173700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>185200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>29300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-235000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1074800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>304500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>23300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
@@ -9390,8 +9607,8 @@
       <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
+      <c r="AD89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE89" s="3">
         <v>0</v>
@@ -9426,8 +9643,11 @@
       <c r="AO89" s="3">
         <v>0</v>
       </c>
+      <c r="AP89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,52 +9689,53 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-246900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-68800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-241900</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-249400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3">
         <v>-143000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9588,8 +9809,11 @@
       <c r="AO91" s="3">
         <v>0</v>
       </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,74 +10053,77 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-332100</v>
+      </c>
+      <c r="E94" s="3">
         <v>48700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>277400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-451700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-88300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>79900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>210100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-295200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-864000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-208200</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-208200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>64900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>147100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-54200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-195300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-238400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>753600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>653400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-258600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1122300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
@@ -9909,8 +10139,8 @@
       <c r="AC94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
@@ -9945,8 +10175,11 @@
       <c r="AO94" s="3">
         <v>0</v>
       </c>
+      <c r="AP94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,8 +10221,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10032,8 +10266,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,74 +10707,77 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-152700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-138000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-60000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-29400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-98500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-94600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-238400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-153500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-109200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-13000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-76500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-52600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-97800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-20000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-50900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-66700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-113300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>13400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
@@ -10547,8 +10793,8 @@
       <c r="AC100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
+      <c r="AD100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -10583,74 +10829,77 @@
       <c r="AO100" s="3">
         <v>0</v>
       </c>
+      <c r="AP100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-8100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-25100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>27500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-18900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-29300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-35600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>23100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-56800</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>-27400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-56800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>9200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-36000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-27400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-56800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>9200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-47300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>23600</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
@@ -10666,8 +10915,8 @@
       <c r="AC101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
+      <c r="AD101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
@@ -10702,74 +10951,77 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-61300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>557500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-276500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>227900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>259900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-238000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>85300</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>85300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>374400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>308200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-57400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-316700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>461100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-582000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>45900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1061900</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
@@ -10785,8 +11037,8 @@
       <c r="AC102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
+      <c r="AD102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE102" s="3">
         <v>0</v>
@@ -10819,6 +11071,9 @@
         <v>0</v>
       </c>
       <c r="AO102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP102" s="3">
         <v>0</v>
       </c>
     </row>
